--- a/players.xlsx
+++ b/players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PL\MLD\FT\evo_fb2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29DC3E0-8807-45A9-A97A-4186D6827F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577BB4E8-7593-469F-9377-E9071D6B6B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
